--- a/DEV/org.openl.rules/test/rules/binding/MethodUsagesMetaInfoTest.xlsx
+++ b/DEV/org.openl.rules/test/rules/binding/MethodUsagesMetaInfoTest.xlsx
@@ -164,7 +164,7 @@
     <t>return value;</t>
   </si>
   <si>
-    <t xml:space="preserve">for (int i = 0; i &lt; 2; i++) {
+    <t xml:space="preserve">for (int i = 0; i &lt; 2; i += 1) {
    value = testDT(i);
 }
 </t>
